--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -1065,12 +1065,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>公表画面（記入日 令和7年10月6日）により、定員100人・入居者97人・入居率100％、要支援1・2が26人（26.8％）、要介護1が42人（43.3％）で、要支援1〜要介護1が68人（70.1％）を占めることが確認された。介護職員31人（常勤15・非常勤16）、介護職員の退職者数11人、昨年度の退居者22人である。</t>
+          <t>公表画面（記入日 令和7年10月6日）により、定員100人・入居者97人、公表画面の「入居率」の欄は100.0％であるが入居者数から計算すると97.0％であり公表資料の中で食い違っている、要支援1・2が26人（26.8％）、要介護1が42人（43.3％）で、要支援1〜要介護1が68人（70.1％）を占めることが確認された。介護職員31人（常勤15・非常勤16）、介護職員の退職者数11人、昨年度の退居者22人である。</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>居所変更実態調査に回答していない区域内最大の特定施設について、定員・入居者数・要介護度別の内訳・従業者数を補うことができた。特定施設は定員156人に対し入居者154人（98.7％）でほぼ満室である。入所前の居場所と退去先は公表されていないため補えない。</t>
+          <t>居所変更実態調査に回答していない区域内最大の特定施設について、定員・入居者数・要介護度別の内訳・従業者数を補うことができた。特定施設は区域内3施設とも入居率が高い（回答2施設98.3％・公表データによる1施設97.0％。時点が異なるため合計の98.7％は参考値）。入所前の居場所と退去先は公表されていないため補えない。</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
